--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562575515</v>
+        <v>46157.93071813641</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93071813641</v>
+        <v>46157.93155497503</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93155497503</v>
+        <v>46157.9339426672</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9339426672</v>
+        <v>46157.93709647123</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93709647123</v>
+        <v>46158.28211185511</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211185511</v>
+        <v>46158.29666638312</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29666638312</v>
+        <v>46158.29806392724</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806392724</v>
+        <v>46158.3338200553</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3338200553</v>
+        <v>46158.3684907983</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3684907983</v>
+        <v>46158.3728214742</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
